--- a/imageCreationExcel/Bright/Master/MASTER_1.xlsx
+++ b/imageCreationExcel/Bright/Master/MASTER_1.xlsx
@@ -552,15 +552,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\1_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>M_1_1_R_filler_1_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_1_1_R_filler_1_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -660,15 +666,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\5_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>M_1_3_S_filler_5_day_rain_busy_MODEL.jpg</t>
+          <t>M_1_3_S_filler_5_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -768,15 +792,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\0_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>M_1_5_E_filler_0_day_sun_busy_MODEL.jpg</t>
+          <t>M_1_5_E_filler_0_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -822,15 +864,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\7_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>M_1_6_7_match_7_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_1_6_7_match_7_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -876,15 +924,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\9_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>M_1_7_G_filler_9_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_1_7_G_filler_9_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -984,15 +1038,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\1_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>M_1_9_9_unmatch_1_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_1_9_9_unmatch_1_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -1038,15 +1098,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\5_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>M_1_10_A_filler_5_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_1_10_A_filler_5_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -1092,15 +1158,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\2_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>M_1_11_2_match_2_day_sun_empty_MODEL.jpg</t>
+          <t>M_1_11_2_match_2_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -1146,15 +1230,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\6_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>M_1_12_Q_filler_6_day_rain_empty_MODEL.jpg</t>
+          <t>M_1_12_Q_filler_6_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1200,15 +1302,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\6_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>M_1_13_6_match_6_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_1_13_6_match_6_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -1254,15 +1362,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\3_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>M_1_14_E_filler_3_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_1_14_E_filler_3_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -1362,15 +1476,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\7_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>M_1_16_5_unmatch_7_day_rain_empty_MODEL.jpg</t>
+          <t>M_1_16_5_unmatch_7_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1470,15 +1602,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\3_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>M_1_18_1_unmatch_3_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_1_18_1_unmatch_3_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -1524,15 +1662,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\3_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>M_1_19_B_filler_3_day_rain_busy_MODEL.jpg</t>
+          <t>M_1_19_B_filler_3_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1578,15 +1734,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>M_1_20_T_filler_7_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_1_20_T_filler_7_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1632,15 +1794,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\7_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>M_1_21_J_filler_7_day_sun_busy_MODEL.jpg</t>
+          <t>M_1_21_J_filler_7_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -1686,15 +1866,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\2_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>M_1_22_E_filler_2_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_1_22_E_filler_2_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1740,15 +1926,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\1_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>M_1_23_1_match_1_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_1_23_1_match_1_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -1848,15 +2040,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\9_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>M_1_25_E_filler_9_day_sun_busy_MODEL.jpg</t>
+          <t>M_1_25_E_filler_9_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -1902,15 +2112,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\8_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>M_1_26_C_filler_8_day_rain_empty_MODEL.jpg</t>
+          <t>M_1_26_C_filler_8_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2010,15 +2238,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\1_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>M_1_28_F_filler_1_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_1_28_F_filler_1_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2064,15 +2298,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\2_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>M_1_29_J_filler_2_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_1_29_J_filler_2_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2358,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\0_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>M_1_30_U_filler_0_day_sun_busy_MODEL.jpg</t>
+          <t>M_1_30_U_filler_0_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2172,15 +2430,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\3_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>M_1_31_3_match_3_day_rain_empty_MODEL.jpg</t>
+          <t>M_1_31_3_match_3_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2280,15 +2556,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\8_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>M_1_33_8_match_8_day_sun_empty_MODEL.jpg</t>
+          <t>M_1_33_8_match_8_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -2334,15 +2628,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\9_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>M_1_34_L_filler_9_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_1_34_L_filler_9_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -2442,15 +2742,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\5_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>M_1_36_R_filler_5_day_rain_empty_MODEL.jpg</t>
+          <t>M_1_36_R_filler_5_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2604,15 +2922,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\2_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>M_1_39_8_unmatch_2_day_sun_busy_MODEL.jpg</t>
+          <t>M_1_39_8_unmatch_2_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2766,15 +3102,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\2_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>M_1_42_F_filler_2_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_1_42_F_filler_2_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -2820,15 +3162,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\8_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>M_1_43_U_filler_8_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_1_43_U_filler_8_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -2928,15 +3276,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\3_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>M_1_45_F_filler_3_day_rain_empty_MODEL.jpg</t>
+          <t>M_1_45_F_filler_3_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -3036,15 +3402,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\2_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>M_1_47_8_unmatch_2_day_sun_busy_MODEL.jpg</t>
+          <t>M_1_47_8_unmatch_2_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
